--- a/data/gravel/Salsa Warbird 2025.xlsx
+++ b/data/gravel/Salsa Warbird 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4A0551-2833-F048-83D4-60C42F011B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561AC07B-D8C8-0644-B874-B5B1FF495DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9500" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5720" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>a8:i33</t>
+  </si>
+  <si>
+    <t>https://www.salsacycles.com/cdn/shop/files/salsa-warbird-c-force-axs-wide-bike-black-BK01421-1920x1080-uc-1.png?v=1738780114</t>
   </si>
 </sst>
 </file>
@@ -778,6 +781,11 @@
         <v>108</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Salsa Warbird 2025.xlsx
+++ b/data/gravel/Salsa Warbird 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561AC07B-D8C8-0644-B874-B5B1FF495DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7A4BE-B3C2-524E-B4D5-AB392AAF6EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5720" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16480" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -368,9 +368,6 @@
     <t>press fit</t>
   </si>
   <si>
-    <t>52/36</t>
-  </si>
-  <si>
     <t>rider_min_spec</t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>https://www.salsacycles.com/cdn/shop/files/salsa-warbird-c-force-axs-wide-bike-black-BK01421-1920x1080-uc-1.png?v=1738780114</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bloomington, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -735,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -783,7 +789,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -791,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1477,7 +1483,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C32">
         <v>150</v>
@@ -1503,7 +1509,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33">
         <v>157</v>
@@ -1699,8 +1705,8 @@
       <c r="A55" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>111</v>
+      <c r="B55" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1742,16 +1748,25 @@
       <c r="A63" t="s">
         <v>81</v>
       </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>82</v>
       </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>83</v>
       </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -1786,11 +1801,17 @@
       <c r="A70" t="s">
         <v>88</v>
       </c>
+      <c r="B70">
+        <v>2199</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>89</v>
       </c>
+      <c r="B71">
+        <v>3199</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -1800,6 +1821,17 @@
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>91</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Salsa Warbird 2025.xlsx
+++ b/data/gravel/Salsa Warbird 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7A4BE-B3C2-524E-B4D5-AB392AAF6EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572B8CBF-FE8E-1E4B-B764-D0617DC68F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16480" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1733,6 +1736,9 @@
       <c r="A60" t="s">
         <v>78</v>
       </c>
+      <c r="B60" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">

--- a/data/gravel/Salsa Warbird 2025.xlsx
+++ b/data/gravel/Salsa Warbird 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572B8CBF-FE8E-1E4B-B764-D0617DC68F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA43A78-F19A-FD45-8EBA-0E0CBB4C020B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -390,6 +390,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -744,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1669,174 +1687,204 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>71</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54">
-        <v>44</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" s="4">
-        <v>52</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" t="s">
-        <v>118</v>
+        <v>72</v>
+      </c>
+      <c r="B60">
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B61" s="4">
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>109</v>
+        <v>78</v>
+      </c>
+      <c r="B66" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>85</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B70">
-        <v>2199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B71">
-        <v>3199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>84</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>115</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>116</v>
       </c>
     </row>
